--- a/results/link-prediction-gcn/Link/1shot/Cora/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/1shot/Cora/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>0.5089±0.0125</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0.4845±0.0116</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0.5212±0.0263</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0.4981±0.0000</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0.4744±0.0000</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.5993±0.0705</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.5294±0.0181</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.5294±0.0181</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.5294±0.0181</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.6388±0.0260</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.5168±0.0172</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.5411±0.0230</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0.5051±0.0072</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>0.5304±0.0429</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0.4851±0.0029</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0.5443±0.0122</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.5484±0.0000</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>0.5484±0.0000</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0.5484±0.0000</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>0.6025±0.0139</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.5003±0.0004</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.5003±0.0004</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.5003±0.0004</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.5645±0.0342</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.6540±0.0751</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>0.4877±0.0000</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.5769±0.0000</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.5278±0.0394</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.5465±0.0657</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.4791±0.0129</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.4997±0.0050</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>0.4877±0.0000</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0.4782±0.0000</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.5955±0.0681</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.5857±0.0645</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.5857±0.0645</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.5857±0.0645</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>0.5974±0.0689</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0.5870±0.0619</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0.5971±0.0697</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.6319±0.0154</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.4826±0.0090</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.5013±0.0172</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.4994±0.0009</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>0.5285±0.0000</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0.5009±0.0000</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0.5009±0.0000</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0.5009±0.0000</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>0.5579±0.0000</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>0.5797±0.0000</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.6338±0.0101</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.6837±0.0073</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.6837±0.0073</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.6837±0.0073</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.6743±0.0220</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.6920±0.0109</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.6825±0.0059</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>0.4987±0.0018</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0.4994±0.0031</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0.4886±0.0154</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>0.5076±0.0000</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>0.5933±0.0661</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>0.5601±0.0565</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>0.5601±0.0565</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>0.5601±0.0565</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>0.5927±0.0662</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.6682±0.0202</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>0.5898±0.0638</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0.4981±0.0020</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>0.5082±0.0308</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.6034±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>0.6034±0.0000</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.6034±0.0000</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>0.5588±0.0000</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>0.6034±0.0000</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>0.5939±0.0683</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>0.5835±0.0592</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>0.5835±0.0592</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>0.5835±0.0592</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>0.5863±0.0613</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>0.5070±0.0081</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>0.5857±0.0648</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0.6357±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.4915±0.0000</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.4896±0.0000</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>0.5237±0.0335</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>0.4978±0.0072</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>0.5244±0.0287</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>0.5000±0.0000</t>
         </is>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0.6167±0.0000</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0.6879±0.0000</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0.6879±0.0000</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.6879±0.0000</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0.6461±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.6300±0.0000</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0.6954±0.0000</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0.5085±0.0000</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>0.6290±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>0.6290±0.0000</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>0.6290±0.0000</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.5066±0.0000</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>0.6195±0.0000</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>0.5901±0.0000</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>0.5901±0.0000</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>0.5901±0.0000</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>0.4972±0.0000</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>0.6025±0.0000</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0.4810±0.0000</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>0.4991±0.0000</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.5000±0.0000</t>
-        </is>
-      </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5977±0.0000</t>
+          <t>0.5408±0.0530</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5171±0.0000</t>
+          <t>0.5076±0.0027</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5171±0.0000</t>
+          <t>0.5076±0.0027</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5171±0.0000</t>
+          <t>0.5076±0.0027</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.6205±0.0000</t>
+          <t>0.5016±0.0012</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5977±0.0000</t>
+          <t>0.5999±0.0334</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5142±0.0000</t>
+          <t>0.5054±0.0024</t>
         </is>
       </c>
     </row>
@@ -1355,457 +1355,457 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>0.6391±0.0391</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>0.6485±0.0129</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0.6604±0.0060</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>0.6650±0.0000</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0.6336±0.0000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.6954±0.0225</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.6783±0.0065</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.6783±0.0065</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.6783±0.0065</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.7066±0.0133</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.6444±0.0274</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.6832±0.0096</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0.6414±0.0357</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>0.6778±0.0157</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0.6341±0.0113</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0.6577±0.0090</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.6844±0.0000</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>0.6844±0.0000</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0.6844±0.0000</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>0.7040±0.0051</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.6668±0.0002</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.6668±0.0002</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.6668±0.0002</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.6937±0.0150</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.7357±0.0377</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0.6498±0.0000</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.6974±0.0000</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.3548±0.2739</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.6755±0.0124</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.6426±0.0146</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.6515±0.0121</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0.6530±0.0000</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0.6391±0.0000</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.6790±0.0143</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.6924±0.0195</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.6924±0.0195</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.6924±0.0195</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>0.6806±0.0101</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>0.6991±0.0239</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>0.6990±0.0229</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0.2222±0.3143</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.7253±0.0086</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.6447±0.0080</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.6431±0.0102</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.6661±0.0008</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.7239±0.0072</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.7474±0.0028</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.7474±0.0028</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.7474±0.0028</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.7458±0.0091</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.7500±0.0081</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.7462±0.0017</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>0.6655±0.0016</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>0.6750±0.0000</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0.6671±0.0000</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.6671±0.0000</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0.6671±0.0000</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>0.6868±0.0000</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0.7033±0.0000</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>0.6637±0.0036</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0.6546±0.0162</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>0.6790±0.0088</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0138</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0138</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>0.6828±0.0138</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.6736±0.0173</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.7413±0.0094</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>0.6937±0.0192</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>0.4444±0.3143</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0.6658±0.0000</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>0.6684±0.0000</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0.6647±0.0022</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>0.6583±0.0142</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AG3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>0.6812±0.0282</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>0.6951±0.0202</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>0.6951±0.0202</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>0.6951±0.0202</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>0.6773±0.0134</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>0.6677±0.0023</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>0.6867±0.0156</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.7010±0.0000</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>0.7010±0.0000</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.7010±0.0000</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>0.6767±0.0141</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>0.6340±0.0196</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>0.6486±0.0092</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>0.6873±0.0000</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>0.7069±0.0000</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>0.6667±0.0000</t>
         </is>
       </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>0.7292±0.0000</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.6582±0.0000</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.6551±0.0000</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>0.7187±0.0000</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>0.7550±0.0000</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>0.7550±0.0000</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>0.7550±0.0000</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>0.7295±0.0000</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>0.7174±0.0000</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>0.7585±0.0000</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0.6696±0.0000</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>0.7071±0.0000</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>0.7071±0.0000</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>0.7071±0.0000</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.6696±0.0000</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>0.6835±0.0000</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>0.0000±0.0000</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BT3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BV3" t="inlineStr">
-        <is>
-          <t>0.6905±0.0000</t>
-        </is>
-      </c>
-      <c r="BW3" t="inlineStr">
-        <is>
-          <t>0.6905±0.0000</t>
-        </is>
-      </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>0.6905±0.0000</t>
-        </is>
-      </c>
-      <c r="BY3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="BZ3" t="inlineStr">
-        <is>
-          <t>0.6641±0.0000</t>
-        </is>
-      </c>
-      <c r="CA3" t="inlineStr">
-        <is>
-          <t>0.6769±0.0000</t>
-        </is>
-      </c>
-      <c r="CB3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>0.6450±0.0000</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>0.6645±0.0000</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>0.6667±0.0000</t>
-        </is>
-      </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.7072±0.0000</t>
+          <t>0.6817±0.0192</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6735±0.0000</t>
+          <t>0.6701±0.0012</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6735±0.0000</t>
+          <t>0.6701±0.0012</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6735±0.0000</t>
+          <t>0.6701±0.0012</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.7122±0.0000</t>
+          <t>0.6674±0.0005</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.7072±0.0000</t>
+          <t>0.7046±0.0112</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6722±0.0000</t>
+          <t>0.6679±0.0000</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.6725±0.0000</t>
+          <t>0.5939±0.0249</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.6827±0.0000</t>
+          <t>0.6797±0.0111</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4794±0.0000</t>
+          <t>0.6332±0.0166</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.5011±0.0000</t>
+          <t>0.6523±0.0308</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.6802±0.0000</t>
+          <t>0.6724±0.0048</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.7000±0.0000</t>
+          <t>0.6726±0.0062</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6785±0.0000</t>
+          <t>0.7127±0.0287</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.6934±0.0000</t>
+          <t>0.7435±0.0069</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.6934±0.0000</t>
+          <t>0.7435±0.0069</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.6934±0.0000</t>
+          <t>0.7435±0.0069</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.6758±0.0000</t>
+          <t>0.7094±0.0280</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.6081±0.0000</t>
+          <t>0.6010±0.0181</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.6934±0.0000</t>
+          <t>0.7496±0.0183</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.5940±0.0000</t>
+          <t>0.5725±0.0243</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.7384±0.0000</t>
+          <t>0.7001±0.0094</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4775±0.0000</t>
+          <t>0.5475±0.0471</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.4726±0.0000</t>
+          <t>0.6529±0.0235</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.6806±0.0000</t>
+          <t>0.6649±0.0027</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.6780±0.0000</t>
+          <t>0.6627±0.0178</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.7366±0.0000</t>
+          <t>0.7572±0.0102</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.7863±0.0000</t>
+          <t>0.8066±0.0181</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.7863±0.0000</t>
+          <t>0.8066±0.0181</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.7863±0.0000</t>
+          <t>0.8066±0.0181</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.7710±0.0000</t>
+          <t>0.7606±0.0089</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8414±0.0000</t>
+          <t>0.8145±0.0333</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.7650±0.0000</t>
+          <t>0.7923±0.0178</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.6210±0.0000</t>
+          <t>0.5328±0.0408</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6817±0.0000</t>
+          <t>0.6885±0.0190</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.4793±0.0000</t>
+          <t>0.6423±0.0197</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.6742±0.0000</t>
+          <t>0.6584±0.0122</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.6789±0.0000</t>
+          <t>0.6701±0.0043</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.6794±0.0000</t>
+          <t>0.6736±0.0051</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.7157±0.0000</t>
+          <t>0.6992±0.0210</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.6980±0.0175</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.6980±0.0175</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.7235±0.0000</t>
+          <t>0.6980±0.0175</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.7154±0.0000</t>
+          <t>0.6949±0.0229</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.7541±0.0000</t>
+          <t>0.7380±0.0550</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.7272±0.0000</t>
+          <t>0.7014±0.0384</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.5572±0.0000</t>
+          <t>0.5358±0.0204</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.8205±0.0000</t>
+          <t>0.7954±0.0177</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4886±0.0000</t>
+          <t>0.6136±0.0126</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4867±0.0000</t>
+          <t>0.6098±0.0426</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.7161±0.0000</t>
+          <t>0.7154±0.0307</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.6863±0.0000</t>
+          <t>0.6813±0.0083</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.7992±0.0000</t>
+          <t>0.7891±0.0093</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.8479±0.0000</t>
+          <t>0.8106±0.0081</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.8479±0.0000</t>
+          <t>0.8106±0.0081</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.8479±0.0000</t>
+          <t>0.8106±0.0081</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.7851±0.0000</t>
+          <t>0.7947±0.0043</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.8180±0.0000</t>
+          <t>0.8419±0.0039</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.8318±0.0000</t>
+          <t>0.8012±0.0109</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.6699±0.0000</t>
+          <t>0.6315±0.0169</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.6875±0.0000</t>
+          <t>0.6805±0.0071</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4851±0.0000</t>
+          <t>0.6492±0.0174</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.6978±0.0000</t>
+          <t>0.6493±0.0168</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.6783±0.0000</t>
+          <t>0.6656±0.0061</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.6802±0.0000</t>
+          <t>0.6691±0.0056</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.6846±0.0000</t>
+          <t>0.6953±0.0146</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.6861±0.0000</t>
+          <t>0.6928±0.0113</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.6861±0.0000</t>
+          <t>0.6928±0.0113</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.6861±0.0000</t>
+          <t>0.6928±0.0113</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.6810±0.0000</t>
+          <t>0.6956±0.0221</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.8313±0.0000</t>
+          <t>0.8208±0.0145</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.6668±0.0000</t>
+          <t>0.6987±0.0234</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.6388±0.0000</t>
+          <t>0.5936±0.0353</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.6863±0.0000</t>
+          <t>0.6849±0.0069</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.4744±0.0000</t>
+          <t>0.6452±0.0259</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.6236±0.0000</t>
+          <t>0.6503±0.0235</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.6764±0.0000</t>
+          <t>0.6677±0.0048</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.6768±0.0000</t>
+          <t>0.6705±0.0083</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.6818±0.0000</t>
+          <t>0.7001±0.0331</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.6646±0.0000</t>
+          <t>0.7042±0.0130</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.6646±0.0000</t>
+          <t>0.7042±0.0130</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.6646±0.0000</t>
+          <t>0.7042±0.0130</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.6821±0.0000</t>
+          <t>0.6947±0.0130</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.6315±0.0000</t>
+          <t>0.6728±0.0424</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.6458±0.0000</t>
+          <t>0.6988±0.0236</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.6043±0.0000</t>
+          <t>0.6101±0.0373</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.7416±0.0000</t>
+          <t>0.7469±0.0061</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4801±0.0000</t>
+          <t>0.5893±0.0463</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4962±0.0000</t>
+          <t>0.5967±0.0449</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.6413±0.0000</t>
+          <t>0.6574±0.0135</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.6138±0.0340</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.7700±0.0000</t>
+          <t>0.7490±0.0189</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7714±0.0032</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7714±0.0032</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.7786±0.0000</t>
+          <t>0.7714±0.0032</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.7669±0.0000</t>
+          <t>0.7742±0.0059</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.7762±0.0000</t>
+          <t>0.7655±0.0138</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.7783±0.0000</t>
+          <t>0.7364±0.0368</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6866±0.0000</t>
+          <t>0.6213±0.0271</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.7211±0.0000</t>
+          <t>0.7113±0.0068</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.4896±0.0000</t>
+          <t>0.6809±0.0199</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5019±0.0000</t>
+          <t>0.6688±0.0323</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.7157±0.0000</t>
+          <t>0.7014±0.0131</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.7244±0.0000</t>
+          <t>0.7032±0.0140</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.7187±0.0000</t>
+          <t>0.7261±0.0168</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.6987±0.0000</t>
+          <t>0.7397±0.0083</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.6987±0.0000</t>
+          <t>0.7397±0.0083</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.6987±0.0000</t>
+          <t>0.7397±0.0083</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.7162±0.0000</t>
+          <t>0.7156±0.0177</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.6609±0.0000</t>
+          <t>0.6309±0.0366</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6880±0.0000</t>
+          <t>0.7375±0.0195</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.6445±0.0000</t>
+          <t>0.6337±0.0221</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.7648±0.0000</t>
+          <t>0.7173±0.0137</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.4886±0.0000</t>
+          <t>0.5561±0.0628</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.4862±0.0000</t>
+          <t>0.6528±0.0379</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.7179±0.0000</t>
+          <t>0.6956±0.0141</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.7135±0.0000</t>
+          <t>0.6804±0.0200</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.7400±0.0000</t>
+          <t>0.7522±0.0053</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.7895±0.0000</t>
+          <t>0.7998±0.0145</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7895±0.0000</t>
+          <t>0.7998±0.0145</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.7895±0.0000</t>
+          <t>0.7998±0.0145</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.7666±0.0000</t>
+          <t>0.7530±0.0080</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.8066±0.0000</t>
+          <t>0.8014±0.0274</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.7598±0.0000</t>
+          <t>0.7805±0.0107</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.6503±0.0000</t>
+          <t>0.5892±0.0321</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.7094±0.0000</t>
+          <t>0.7145±0.0003</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.4896±0.0000</t>
+          <t>0.6762±0.0282</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.6918±0.0000</t>
+          <t>0.6985±0.0163</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.7120±0.0000</t>
+          <t>0.7020±0.0105</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.7111±0.0000</t>
+          <t>0.6983±0.0113</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.7467±0.0000</t>
+          <t>0.7116±0.0140</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.7160±0.0000</t>
+          <t>0.7126±0.0042</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.7160±0.0000</t>
+          <t>0.7126±0.0042</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.7160±0.0000</t>
+          <t>0.7126±0.0042</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.7543±0.0000</t>
+          <t>0.7082±0.0147</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.7589±0.0000</t>
+          <t>0.7549±0.0444</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.7220±0.0000</t>
+          <t>0.7096±0.0208</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.6037±0.0000</t>
+          <t>0.6084±0.0094</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.8178±0.0000</t>
+          <t>0.7869±0.0167</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.4943±0.0000</t>
+          <t>0.6191±0.0178</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.4934±0.0000</t>
+          <t>0.6030±0.0520</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.7323±0.0000</t>
+          <t>0.7308±0.0315</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.7221±0.0000</t>
+          <t>0.7103±0.0168</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.7957±0.0000</t>
+          <t>0.7812±0.0082</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.8415±0.0000</t>
+          <t>0.7969±0.0159</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.8415±0.0000</t>
+          <t>0.7969±0.0159</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.8415±0.0000</t>
+          <t>0.7969±0.0159</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.7716±0.0000</t>
+          <t>0.7787±0.0096</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.8249±0.0000</t>
+          <t>0.8408±0.0074</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.8190±0.0000</t>
+          <t>0.7859±0.0168</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.6903±0.0000</t>
+          <t>0.6491±0.0138</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.7222±0.0000</t>
+          <t>0.7067±0.0123</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.4927±0.0000</t>
+          <t>0.6848±0.0237</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.7373±0.0000</t>
+          <t>0.6886±0.0320</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.7129±0.0000</t>
+          <t>0.7002±0.0101</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.7140±0.0000</t>
+          <t>0.6997±0.0152</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.7205±0.0000</t>
+          <t>0.7080±0.0131</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6738±0.0000</t>
+          <t>0.7045±0.0071</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6738±0.0000</t>
+          <t>0.7045±0.0071</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6738±0.0000</t>
+          <t>0.7045±0.0071</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.7182±0.0000</t>
+          <t>0.7099±0.0197</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.8129±0.0000</t>
+          <t>0.8126±0.0172</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.6670±0.0000</t>
+          <t>0.7069±0.0016</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.6520±0.0000</t>
+          <t>0.6028±0.0360</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.7209±0.0000</t>
+          <t>0.7093±0.0143</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.4870±0.0000</t>
+          <t>0.6725±0.0437</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.6570±0.0000</t>
+          <t>0.6827±0.0101</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.7105±0.0000</t>
+          <t>0.6985±0.0135</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.7123±0.0000</t>
+          <t>0.7008±0.0156</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.7188±0.0000</t>
+          <t>0.7119±0.0333</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.6519±0.0000</t>
+          <t>0.7129±0.0106</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.6519±0.0000</t>
+          <t>0.7129±0.0106</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.6519±0.0000</t>
+          <t>0.7129±0.0106</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.7189±0.0000</t>
+          <t>0.7081±0.0172</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.6797±0.0000</t>
+          <t>0.7141±0.0461</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6450±0.0000</t>
+          <t>0.7037±0.0259</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.6345±0.0000</t>
+          <t>0.6324±0.0398</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.7581±0.0000</t>
+          <t>0.7461±0.0074</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.4902±0.0000</t>
+          <t>0.5802±0.0414</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.4981±0.0000</t>
+          <t>0.5768±0.0362</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.6663±0.0000</t>
+          <t>0.6658±0.0352</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6674±0.0000</t>
+          <t>0.6301±0.0558</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.7598±0.0000</t>
+          <t>0.7469±0.0307</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.7385±0.0000</t>
+          <t>0.7349±0.0177</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.7385±0.0000</t>
+          <t>0.7349±0.0177</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.7385±0.0000</t>
+          <t>0.7349±0.0177</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.7705±0.0000</t>
+          <t>0.7756±0.0118</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.7722±0.0000</t>
+          <t>0.7613±0.0176</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.7341±0.0000</t>
+          <t>0.7001±0.0196</t>
         </is>
       </c>
     </row>
